--- a/inspection_forms/039_ingredient_contaminant_alert_report_form--inspection_forms.xlsx
+++ b/inspection_forms/039_ingredient_contaminant_alert_report_form--inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,8 +665,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,12 +694,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'type_a'}</t>
+          <t>type_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Type A'}</t>
+          <t>Type A</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'type_b'}</t>
+          <t>type_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Type B'}</t>
+          <t>Type B</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'type_c'}</t>
+          <t>type_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Type C'}</t>
+          <t>Type C</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'room_a'}</t>
+          <t>room_a</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Room A'}</t>
+          <t>Room A</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'room_b'}</t>
+          <t>room_b</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Room B'}</t>
+          <t>Room B</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'room_c'}</t>
+          <t>room_c</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Room C'}</t>
+          <t>Room C</t>
         </is>
       </c>
     </row>
